--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796669</v>
+        <v>119796655</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538585</v>
+        <v>538591</v>
       </c>
       <c r="R5" t="n">
-        <v>6865680</v>
+        <v>6865700</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796656</v>
+        <v>119796662</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538601</v>
+        <v>538598</v>
       </c>
       <c r="R6" t="n">
-        <v>6865690</v>
+        <v>6865700</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796661</v>
+        <v>119796670</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538568</v>
+        <v>538575</v>
       </c>
       <c r="R8" t="n">
-        <v>6865660</v>
+        <v>6865670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796673</v>
+        <v>119796669</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538557</v>
+        <v>538585</v>
       </c>
       <c r="R9" t="n">
-        <v>6865640</v>
+        <v>6865680</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796664</v>
+        <v>119796665</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538622</v>
+        <v>538591</v>
       </c>
       <c r="R10" t="n">
-        <v>6865740</v>
+        <v>6865690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119796672</v>
+        <v>119796654</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538574</v>
+        <v>538571</v>
       </c>
       <c r="R11" t="n">
-        <v>6865670</v>
+        <v>6865700</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119796658</v>
+        <v>119796673</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538596</v>
+        <v>538557</v>
       </c>
       <c r="R12" t="n">
-        <v>6865690</v>
+        <v>6865640</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119796666</v>
+        <v>119796656</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538587</v>
+        <v>538601</v>
       </c>
       <c r="R13" t="n">
         <v>6865690</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119796674</v>
+        <v>119796664</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538532</v>
+        <v>538622</v>
       </c>
       <c r="R14" t="n">
-        <v>6865620</v>
+        <v>6865740</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119796659</v>
+        <v>119796661</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538584</v>
+        <v>538568</v>
       </c>
       <c r="R15" t="n">
-        <v>6865670</v>
+        <v>6865660</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119796654</v>
+        <v>119796659</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538571</v>
+        <v>538584</v>
       </c>
       <c r="R16" t="n">
-        <v>6865700</v>
+        <v>6865670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119796655</v>
+        <v>119796674</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538591</v>
+        <v>538532</v>
       </c>
       <c r="R17" t="n">
-        <v>6865700</v>
+        <v>6865620</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119796662</v>
+        <v>119796666</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538598</v>
+        <v>538587</v>
       </c>
       <c r="R18" t="n">
-        <v>6865700</v>
+        <v>6865690</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796670</v>
+        <v>119796672</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538575</v>
+        <v>538574</v>
       </c>
       <c r="R20" t="n">
         <v>6865670</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119796665</v>
+        <v>119796658</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538591</v>
+        <v>538596</v>
       </c>
       <c r="R21" t="n">
         <v>6865690</v>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796655</v>
+        <v>119796660</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538591</v>
+        <v>538577</v>
       </c>
       <c r="R5" t="n">
-        <v>6865700</v>
+        <v>6865660</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796662</v>
+        <v>119796654</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538598</v>
+        <v>538571</v>
       </c>
       <c r="R6" t="n">
         <v>6865700</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796663</v>
+        <v>119796662</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538589</v>
+        <v>538598</v>
       </c>
       <c r="R7" t="n">
-        <v>6865720</v>
+        <v>6865700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796670</v>
+        <v>119796673</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538575</v>
+        <v>538557</v>
       </c>
       <c r="R8" t="n">
-        <v>6865670</v>
+        <v>6865640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796669</v>
+        <v>119796666</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538585</v>
+        <v>538587</v>
       </c>
       <c r="R9" t="n">
-        <v>6865680</v>
+        <v>6865690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796665</v>
+        <v>119796674</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538591</v>
+        <v>538532</v>
       </c>
       <c r="R10" t="n">
-        <v>6865690</v>
+        <v>6865620</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119796654</v>
+        <v>119796664</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538571</v>
+        <v>538622</v>
       </c>
       <c r="R11" t="n">
-        <v>6865700</v>
+        <v>6865740</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119796673</v>
+        <v>119796658</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538557</v>
+        <v>538596</v>
       </c>
       <c r="R12" t="n">
-        <v>6865640</v>
+        <v>6865690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119796656</v>
+        <v>119796665</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538601</v>
+        <v>538591</v>
       </c>
       <c r="R13" t="n">
         <v>6865690</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119796664</v>
+        <v>119796669</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538622</v>
+        <v>538585</v>
       </c>
       <c r="R14" t="n">
-        <v>6865740</v>
+        <v>6865680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119796661</v>
+        <v>119796670</v>
       </c>
       <c r="B15" t="n">
         <v>97907</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538568</v>
+        <v>538575</v>
       </c>
       <c r="R15" t="n">
-        <v>6865660</v>
+        <v>6865670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119796659</v>
+        <v>119796656</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538584</v>
+        <v>538601</v>
       </c>
       <c r="R16" t="n">
-        <v>6865670</v>
+        <v>6865690</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119796674</v>
+        <v>119796655</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538532</v>
+        <v>538591</v>
       </c>
       <c r="R17" t="n">
-        <v>6865620</v>
+        <v>6865700</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119796666</v>
+        <v>119796672</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538587</v>
+        <v>538574</v>
       </c>
       <c r="R18" t="n">
-        <v>6865690</v>
+        <v>6865670</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119796660</v>
+        <v>119796663</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538577</v>
+        <v>538589</v>
       </c>
       <c r="R19" t="n">
-        <v>6865660</v>
+        <v>6865720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796672</v>
+        <v>119796661</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538574</v>
+        <v>538568</v>
       </c>
       <c r="R20" t="n">
-        <v>6865670</v>
+        <v>6865660</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119796658</v>
+        <v>119796659</v>
       </c>
       <c r="B21" t="n">
         <v>97907</v>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538596</v>
+        <v>538584</v>
       </c>
       <c r="R21" t="n">
-        <v>6865690</v>
+        <v>6865670</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796660</v>
+        <v>119796673</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538577</v>
+        <v>538557</v>
       </c>
       <c r="R5" t="n">
-        <v>6865660</v>
+        <v>6865640</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796654</v>
+        <v>119796666</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538571</v>
+        <v>538587</v>
       </c>
       <c r="R6" t="n">
-        <v>6865700</v>
+        <v>6865690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796662</v>
+        <v>119796669</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538598</v>
+        <v>538585</v>
       </c>
       <c r="R7" t="n">
-        <v>6865700</v>
+        <v>6865680</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796673</v>
+        <v>119796660</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538557</v>
+        <v>538577</v>
       </c>
       <c r="R8" t="n">
-        <v>6865640</v>
+        <v>6865660</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796666</v>
+        <v>119796656</v>
       </c>
       <c r="B9" t="n">
         <v>97907</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538587</v>
+        <v>538601</v>
       </c>
       <c r="R9" t="n">
         <v>6865690</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796674</v>
+        <v>119796661</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538532</v>
+        <v>538568</v>
       </c>
       <c r="R10" t="n">
-        <v>6865620</v>
+        <v>6865660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119796664</v>
+        <v>119796674</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538622</v>
+        <v>538532</v>
       </c>
       <c r="R11" t="n">
-        <v>6865740</v>
+        <v>6865620</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119796658</v>
+        <v>119796662</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538596</v>
+        <v>538598</v>
       </c>
       <c r="R12" t="n">
-        <v>6865690</v>
+        <v>6865700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119796665</v>
+        <v>119796664</v>
       </c>
       <c r="B13" t="n">
         <v>97907</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538591</v>
+        <v>538622</v>
       </c>
       <c r="R13" t="n">
-        <v>6865690</v>
+        <v>6865740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119796669</v>
+        <v>119796665</v>
       </c>
       <c r="B14" t="n">
         <v>97907</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538585</v>
+        <v>538591</v>
       </c>
       <c r="R14" t="n">
-        <v>6865680</v>
+        <v>6865690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119796656</v>
+        <v>119796663</v>
       </c>
       <c r="B16" t="n">
         <v>97907</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538601</v>
+        <v>538589</v>
       </c>
       <c r="R16" t="n">
-        <v>6865690</v>
+        <v>6865720</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119796655</v>
+        <v>119796658</v>
       </c>
       <c r="B17" t="n">
         <v>97907</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538591</v>
+        <v>538596</v>
       </c>
       <c r="R17" t="n">
-        <v>6865700</v>
+        <v>6865690</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119796672</v>
+        <v>119796654</v>
       </c>
       <c r="B18" t="n">
         <v>97907</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538574</v>
+        <v>538571</v>
       </c>
       <c r="R18" t="n">
-        <v>6865670</v>
+        <v>6865700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119796663</v>
+        <v>119796672</v>
       </c>
       <c r="B19" t="n">
         <v>97907</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538589</v>
+        <v>538574</v>
       </c>
       <c r="R19" t="n">
-        <v>6865720</v>
+        <v>6865670</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796661</v>
+        <v>119796655</v>
       </c>
       <c r="B20" t="n">
         <v>97907</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538568</v>
+        <v>538591</v>
       </c>
       <c r="R20" t="n">
-        <v>6865660</v>
+        <v>6865700</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796673</v>
+        <v>119796672</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538557</v>
+        <v>538574</v>
       </c>
       <c r="R5" t="n">
-        <v>6865640</v>
+        <v>6865670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796666</v>
+        <v>119796663</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538587</v>
+        <v>538589</v>
       </c>
       <c r="R6" t="n">
-        <v>6865690</v>
+        <v>6865720</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796669</v>
+        <v>119796659</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538585</v>
+        <v>538584</v>
       </c>
       <c r="R7" t="n">
-        <v>6865680</v>
+        <v>6865670</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796660</v>
+        <v>119796655</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538577</v>
+        <v>538591</v>
       </c>
       <c r="R8" t="n">
-        <v>6865660</v>
+        <v>6865700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796656</v>
+        <v>119796658</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538601</v>
+        <v>538596</v>
       </c>
       <c r="R9" t="n">
         <v>6865690</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796661</v>
+        <v>119796660</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538568</v>
+        <v>538577</v>
       </c>
       <c r="R10" t="n">
         <v>6865660</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119796674</v>
+        <v>119796654</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538532</v>
+        <v>538571</v>
       </c>
       <c r="R11" t="n">
-        <v>6865620</v>
+        <v>6865700</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119796662</v>
+        <v>119796661</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538598</v>
+        <v>538568</v>
       </c>
       <c r="R12" t="n">
-        <v>6865700</v>
+        <v>6865660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119796664</v>
+        <v>119796674</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538622</v>
+        <v>538532</v>
       </c>
       <c r="R13" t="n">
-        <v>6865740</v>
+        <v>6865620</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,10 +2007,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119796665</v>
+        <v>119796669</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538591</v>
+        <v>538585</v>
       </c>
       <c r="R14" t="n">
-        <v>6865690</v>
+        <v>6865680</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
         <v>119796670</v>
       </c>
       <c r="B15" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119796663</v>
+        <v>119796673</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538589</v>
+        <v>538557</v>
       </c>
       <c r="R16" t="n">
-        <v>6865720</v>
+        <v>6865640</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119796658</v>
+        <v>119796664</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538596</v>
+        <v>538622</v>
       </c>
       <c r="R17" t="n">
-        <v>6865690</v>
+        <v>6865740</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119796654</v>
+        <v>119796666</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538571</v>
+        <v>538587</v>
       </c>
       <c r="R18" t="n">
-        <v>6865700</v>
+        <v>6865690</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,10 +2562,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119796672</v>
+        <v>119796665</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538574</v>
+        <v>538591</v>
       </c>
       <c r="R19" t="n">
-        <v>6865670</v>
+        <v>6865690</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,10 +2673,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796655</v>
+        <v>119796656</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538591</v>
+        <v>538601</v>
       </c>
       <c r="R20" t="n">
-        <v>6865700</v>
+        <v>6865690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,10 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119796659</v>
+        <v>119796662</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538584</v>
+        <v>538598</v>
       </c>
       <c r="R21" t="n">
-        <v>6865670</v>
+        <v>6865700</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796672</v>
+        <v>119796665</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538574</v>
+        <v>538591</v>
       </c>
       <c r="R5" t="n">
-        <v>6865670</v>
+        <v>6865690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796663</v>
+        <v>119796666</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538589</v>
+        <v>538587</v>
       </c>
       <c r="R6" t="n">
-        <v>6865720</v>
+        <v>6865690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796659</v>
+        <v>119796663</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538584</v>
+        <v>538589</v>
       </c>
       <c r="R7" t="n">
-        <v>6865670</v>
+        <v>6865720</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796655</v>
+        <v>119796674</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538591</v>
+        <v>538532</v>
       </c>
       <c r="R8" t="n">
-        <v>6865700</v>
+        <v>6865620</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796658</v>
+        <v>119796656</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538596</v>
+        <v>538601</v>
       </c>
       <c r="R9" t="n">
         <v>6865690</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796660</v>
+        <v>119796673</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538577</v>
+        <v>538557</v>
       </c>
       <c r="R10" t="n">
-        <v>6865660</v>
+        <v>6865640</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119796654</v>
+        <v>119796672</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538571</v>
+        <v>538574</v>
       </c>
       <c r="R11" t="n">
-        <v>6865700</v>
+        <v>6865670</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119796661</v>
+        <v>119796658</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538568</v>
+        <v>538596</v>
       </c>
       <c r="R12" t="n">
-        <v>6865660</v>
+        <v>6865690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119796674</v>
+        <v>119796664</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538532</v>
+        <v>538622</v>
       </c>
       <c r="R13" t="n">
-        <v>6865620</v>
+        <v>6865740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119796669</v>
+        <v>119796659</v>
       </c>
       <c r="B14" t="n">
         <v>97930</v>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538585</v>
+        <v>538584</v>
       </c>
       <c r="R14" t="n">
-        <v>6865680</v>
+        <v>6865670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119796670</v>
+        <v>119796654</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538575</v>
+        <v>538571</v>
       </c>
       <c r="R15" t="n">
-        <v>6865670</v>
+        <v>6865700</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119796673</v>
+        <v>119796670</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538557</v>
+        <v>538575</v>
       </c>
       <c r="R16" t="n">
-        <v>6865640</v>
+        <v>6865670</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119796664</v>
+        <v>119796669</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538622</v>
+        <v>538585</v>
       </c>
       <c r="R17" t="n">
-        <v>6865740</v>
+        <v>6865680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119796666</v>
+        <v>119796661</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538587</v>
+        <v>538568</v>
       </c>
       <c r="R18" t="n">
-        <v>6865690</v>
+        <v>6865660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119796665</v>
+        <v>119796662</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538591</v>
+        <v>538598</v>
       </c>
       <c r="R19" t="n">
-        <v>6865690</v>
+        <v>6865700</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,7 +2673,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796656</v>
+        <v>119796660</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538601</v>
+        <v>538577</v>
       </c>
       <c r="R20" t="n">
-        <v>6865690</v>
+        <v>6865660</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119796662</v>
+        <v>119796655</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>538598</v>
+        <v>538591</v>
       </c>
       <c r="R21" t="n">
         <v>6865700</v>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3005,6 +3005,129 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126034603</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57017</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tofsvipa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Vanellus vanellus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kullberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>538532</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6865821</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3010,7 +3010,7 @@
         <v>126034603</v>
       </c>
       <c r="B23" t="n">
-        <v>57017</v>
+        <v>57018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3010,7 +3010,7 @@
         <v>126034603</v>
       </c>
       <c r="B23" t="n">
-        <v>57018</v>
+        <v>57022</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3010,7 +3010,7 @@
         <v>126034603</v>
       </c>
       <c r="B23" t="n">
-        <v>57022</v>
+        <v>57023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>126914233</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>126914244</v>
       </c>
       <c r="B25" t="n">
-        <v>58334</v>
+        <v>58338</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>126914238</v>
       </c>
       <c r="B26" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>126914233</v>
       </c>
       <c r="B24" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>126914244</v>
       </c>
       <c r="B25" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>126914238</v>
       </c>
       <c r="B26" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3485,6 +3485,137 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129308296</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57089</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>102952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tofsvipa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Vanellus vanellus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mörtberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>538533</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6865819</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>07:03</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Calluna AB C250015b</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elvira Klang</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3490,7 +3490,7 @@
         <v>129308296</v>
       </c>
       <c r="B27" t="n">
-        <v>57089</v>
+        <v>57091</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3490,7 +3490,7 @@
         <v>129308296</v>
       </c>
       <c r="B27" t="n">
-        <v>57091</v>
+        <v>57094</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3490,7 +3490,7 @@
         <v>129308296</v>
       </c>
       <c r="B27" t="n">
-        <v>57094</v>
+        <v>57099</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3490,7 +3490,7 @@
         <v>129308296</v>
       </c>
       <c r="B27" t="n">
-        <v>57099</v>
+        <v>57100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -3133,7 +3133,7 @@
         <v>126914233</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>126914244</v>
       </c>
       <c r="B25" t="n">
-        <v>58340</v>
+        <v>58334</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>126914238</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113888477</v>
+        <v>117398821</v>
       </c>
       <c r="B2" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538618</v>
+        <v>538590</v>
       </c>
       <c r="R2" t="n">
-        <v>6865760</v>
+        <v>6865782</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117398701</v>
+        <v>126034603</v>
       </c>
       <c r="B3" t="n">
-        <v>79069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>102952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,19 +814,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538590</v>
+        <v>538532</v>
       </c>
       <c r="R3" t="n">
-        <v>6865782</v>
+        <v>6865821</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,49 +892,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117398821</v>
+        <v>129308296</v>
       </c>
       <c r="B4" t="n">
-        <v>78216</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>102952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,16 +937,31 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Mörtberget, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538590</v>
+        <v>538533</v>
       </c>
       <c r="R4" t="n">
-        <v>6865782</v>
+        <v>6865819</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,17 +988,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Calluna AB C250015b</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,69 +1023,72 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Marta Lomas Vega</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Elvira Klang</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796665</v>
+        <v>126914235</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102980</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538591</v>
+        <v>538630</v>
       </c>
       <c r="R5" t="n">
-        <v>6865690</v>
+        <v>6865798</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,17 +1112,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,69 +1142,72 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796666</v>
+        <v>126914238</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538587</v>
+        <v>538630</v>
       </c>
       <c r="R6" t="n">
-        <v>6865690</v>
+        <v>6865798</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,17 +1231,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,66 +1261,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796663</v>
+        <v>124579641</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>538589</v>
+        <v>538575</v>
       </c>
       <c r="R7" t="n">
-        <v>6865720</v>
+        <v>6865809</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,17 +1338,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,49 +1368,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796674</v>
+        <v>126914233</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1379,19 +1413,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538532</v>
+        <v>538630</v>
       </c>
       <c r="R8" t="n">
-        <v>6865620</v>
+        <v>6865798</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,17 +1457,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,69 +1487,72 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796656</v>
+        <v>126914244</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Backarvall, Hls</t>
+          <t>Kullberget, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>538601</v>
+        <v>538630</v>
       </c>
       <c r="R9" t="n">
-        <v>6865690</v>
+        <v>6865798</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,17 +1576,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,27 +1606,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Mova Hebert</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796673</v>
+        <v>113888477</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1607,13 +1657,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>538557</v>
+        <v>538618</v>
       </c>
       <c r="R10" t="n">
-        <v>6865640</v>
+        <v>6865760</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,12 +1687,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,15 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119796672</v>
+        <v>119796654</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1754,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>538574</v>
+        <v>538571</v>
       </c>
       <c r="R11" t="n">
-        <v>6865670</v>
+        <v>6865700</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,15 +1830,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119796658</v>
+        <v>119796655</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1820,7 +1860,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1829,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>538596</v>
+        <v>538591</v>
       </c>
       <c r="R12" t="n">
-        <v>6865690</v>
+        <v>6865700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,15 +1936,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119796664</v>
+        <v>119796656</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,7 +1966,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,10 +1975,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>538622</v>
+        <v>538601</v>
       </c>
       <c r="R13" t="n">
-        <v>6865740</v>
+        <v>6865690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,15 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119796659</v>
+        <v>119796658</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,10 +2081,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>538584</v>
+        <v>538596</v>
       </c>
       <c r="R14" t="n">
-        <v>6865670</v>
+        <v>6865690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,15 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119796654</v>
+        <v>119796659</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2153,7 +2178,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2162,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538571</v>
+        <v>538584</v>
       </c>
       <c r="R15" t="n">
-        <v>6865700</v>
+        <v>6865670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,15 +2254,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119796670</v>
+        <v>119796660</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2264,7 +2284,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2273,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538575</v>
+        <v>538577</v>
       </c>
       <c r="R16" t="n">
-        <v>6865670</v>
+        <v>6865660</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,15 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119796669</v>
+        <v>119796661</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,7 +2390,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>538585</v>
+        <v>538568</v>
       </c>
       <c r="R17" t="n">
-        <v>6865680</v>
+        <v>6865660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2451,15 +2466,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119796661</v>
+        <v>119796662</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2486,7 +2496,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2495,10 +2505,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>538568</v>
+        <v>538598</v>
       </c>
       <c r="R18" t="n">
-        <v>6865660</v>
+        <v>6865700</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2562,15 +2572,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119796662</v>
+        <v>119796663</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>538598</v>
+        <v>538589</v>
       </c>
       <c r="R19" t="n">
-        <v>6865700</v>
+        <v>6865720</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,15 +2678,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119796660</v>
+        <v>119796664</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2717,10 +2717,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>538577</v>
+        <v>538622</v>
       </c>
       <c r="R20" t="n">
-        <v>6865660</v>
+        <v>6865740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2784,15 +2784,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119796655</v>
+        <v>119796665</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2814,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2831,7 +2826,7 @@
         <v>538591</v>
       </c>
       <c r="R21" t="n">
-        <v>6865700</v>
+        <v>6865690</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,50 +2890,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124579641</v>
+        <v>119796666</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kullberget, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>538575</v>
+        <v>538587</v>
       </c>
       <c r="R22" t="n">
-        <v>6865809</v>
+        <v>6865690</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,22 +2959,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>09:57</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2995,22 +2984,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126034603</v>
+        <v>119796669</v>
       </c>
       <c r="B23" t="n">
-        <v>57023</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,21 +3007,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102952</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3040,31 +3029,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kullberget, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>538532</v>
+        <v>538585</v>
       </c>
       <c r="R23" t="n">
-        <v>6865821</v>
+        <v>6865680</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3088,22 +3065,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:10</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:10</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3118,44 +3090,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126914233</v>
+        <v>119796670</v>
       </c>
       <c r="B24" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3163,27 +3135,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kullberget, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>538630</v>
+        <v>538575</v>
       </c>
       <c r="R24" t="n">
-        <v>6865798</v>
+        <v>6865670</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3207,22 +3171,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>07:55</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>07:55</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3237,72 +3196,64 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126914244</v>
+        <v>119796672</v>
       </c>
       <c r="B25" t="n">
-        <v>58340</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kullberget, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538630</v>
+        <v>538574</v>
       </c>
       <c r="R25" t="n">
-        <v>6865798</v>
+        <v>6865670</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,22 +3277,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>08:15</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>08:16</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,44 +3302,44 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126914238</v>
+        <v>119796673</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3401,27 +3347,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullberget, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538630</v>
+        <v>538557</v>
       </c>
       <c r="R26" t="n">
-        <v>6865798</v>
+        <v>6865640</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,22 +3383,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>08:04</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>08:04</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,22 +3408,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Mova Hebert</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129308296</v>
+        <v>119796674</v>
       </c>
       <c r="B27" t="n">
-        <v>57100</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3498,21 +3431,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102952</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3520,31 +3453,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörtberget, Hls</t>
+          <t>Backarvall, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>538533</v>
+        <v>538532</v>
       </c>
       <c r="R27" t="n">
-        <v>6865819</v>
+        <v>6865620</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3571,27 +3489,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>07:03</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>07:05</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Calluna AB C250015b</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,15 +3514,121 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marta Lomas Vega</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elvira Klang</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>117398701</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Backarvall, Hls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>538590</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6865782</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Färila</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21134-2024 artfynd.xlsx
+++ b/artfynd/A 21134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126034603</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129308296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1032,6 +1047,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796674</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398821</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914235</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914238</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1483,6 +1518,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124579641</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914233</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1721,6 +1766,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126914244</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1827,6 +1877,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888477</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1933,6 +1988,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796654</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2039,6 +2099,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796655</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2145,6 +2210,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796656</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2251,6 +2321,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796658</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2357,6 +2432,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796659</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2463,6 +2543,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796660</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2569,6 +2654,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796661</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2675,6 +2765,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796662</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2781,6 +2876,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796663</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2887,6 +2987,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796664</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2993,6 +3098,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796665</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3099,6 +3209,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796666</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3205,6 +3320,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796669</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3311,6 +3431,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796670</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3417,6 +3542,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796672</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3523,6 +3653,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119796673</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3629,8 +3764,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117398701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>